--- a/web/public/samples/invoices.xlsx
+++ b/web/public/samples/invoices.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5186" uniqueCount="1401">
   <si>
-    <t>Invoice register — Q4 2026</t>
+    <t>Invoice register: Q4 2026</t>
   </si>
   <si>
     <t>No.</t>
